--- a/public/templates/04_차량운행일지_미수금관리/기중기_배차일보_미수금_수당관리.xlsx
+++ b/public/templates/04_차량운행일지_미수금관리/기중기_배차일보_미수금_수당관리.xlsx
@@ -1413,9 +1413,21 @@
       <c r="D3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>△△건설</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>최소장</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>010-0000-2222</t>
+        </is>
+      </c>
       <c r="D4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1873,198 +1885,302 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13"/>
-      <c r="B3" s="10"/>
+      <c r="A3" s="13" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>경기00가1234</t>
+        </is>
+      </c>
       <c r="C3" s="14" t="str">
         <f aca="false">IF($B3="","",IFERROR(INDEX(차량목록!$B$3:$B$42,MATCH($B3,차량목록!$A$3:$A$42,0)),"미등록차량"))</f>
-        <v/>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="16" t="str">
+        <v>김기사</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>○○종합건설</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>○○아파트 신축 자재 양중</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>1730</v>
+      </c>
+      <c r="H3" s="16" t="n">
         <f aca="false">IF(OR($F3="",$G3=""),"",ROUND(IF($G3&lt;1,$G3*24,INT($G3/100)+MOD($G3,100)/60)-IF($F3&lt;1,$F3*24,INT($F3/100)+MOD($F3,100)/60),2))</f>
-        <v/>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="18" t="str">
+        <v>9.5</v>
+      </c>
+      <c r="I3" s="17" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J3" s="18" t="n">
         <f aca="false">IF(OR($H3="",$I3=""),"",ROUND($H3*$I3,0))</f>
-        <v/>
-      </c>
-      <c r="K3" s="13"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="18" t="str">
+        <v>1140000</v>
+      </c>
+      <c r="K3" s="13" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L3" s="17" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="M3" s="18" t="n">
         <f aca="false">IF($J3="","",$J3-IF($L3="",0,$L3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N3" s="19" t="str">
         <f aca="true">IF(OR($A3="",$M3="",$M3&lt;=0),"",TODAY()-$A3)</f>
         <v/>
       </c>
-      <c r="O3" s="20" t="str">
+      <c r="O3" s="20" t="n">
         <f aca="false">IF($B3="","",IFERROR(INDEX(차량목록!$D$3:$D$42,MATCH($B3,차량목록!$A$3:$A$42,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P3" s="18" t="str">
+        <v>0.25</v>
+      </c>
+      <c r="P3" s="18" t="n">
         <f aca="false">IF($J3="","",ROUND($J3*$O3,0))</f>
-        <v/>
+        <v>285000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13"/>
-      <c r="B4" s="10"/>
+      <c r="A4" s="13" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>경기00가5678</t>
+        </is>
+      </c>
       <c r="C4" s="14" t="str">
         <f aca="false">IF($B4="","",IFERROR(INDEX(차량목록!$B$3:$B$42,MATCH($B4,차량목록!$A$3:$A$42,0)),"미등록차량"))</f>
-        <v/>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="16" t="str">
+        <v>이기사</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>○○종합건설</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>철골 설치</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H4" s="16" t="n">
         <f aca="false">IF(OR($F4="",$G4=""),"",ROUND(IF($G4&lt;1,$G4*24,INT($G4/100)+MOD($G4,100)/60)-IF($F4&lt;1,$F4*24,INT($F4/100)+MOD($F4,100)/60),2))</f>
-        <v/>
-      </c>
-      <c r="I4" s="17"/>
-      <c r="J4" s="18" t="str">
+        <v>9</v>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J4" s="18" t="n">
         <f aca="false">IF(OR($H4="",$I4=""),"",ROUND($H4*$I4,0))</f>
-        <v/>
+        <v>1350000</v>
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="17"/>
-      <c r="M4" s="18" t="str">
+      <c r="M4" s="18" t="n">
         <f aca="false">IF($J4="","",$J4-IF($L4="",0,$L4))</f>
-        <v/>
-      </c>
-      <c r="N4" s="19" t="str">
+        <v>1350000</v>
+      </c>
+      <c r="N4" s="19" t="n">
         <f aca="true">IF(OR($A4="",$M4="",$M4&lt;=0),"",TODAY()-$A4)</f>
-        <v/>
-      </c>
-      <c r="O4" s="20" t="str">
+        <v>33</v>
+      </c>
+      <c r="O4" s="20" t="n">
         <f aca="false">IF($B4="","",IFERROR(INDEX(차량목록!$D$3:$D$42,MATCH($B4,차량목록!$A$3:$A$42,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P4" s="18" t="str">
+        <v>0.2</v>
+      </c>
+      <c r="P4" s="18" t="n">
         <f aca="false">IF($J4="","",ROUND($J4*$O4,0))</f>
-        <v/>
+        <v>270000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13"/>
-      <c r="B5" s="10"/>
+      <c r="A5" s="13" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>경기00가1234</t>
+        </is>
+      </c>
       <c r="C5" s="14" t="str">
         <f aca="false">IF($B5="","",IFERROR(INDEX(차량목록!$B$3:$B$42,MATCH($B5,차량목록!$A$3:$A$42,0)),"미등록차량"))</f>
-        <v/>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="16" t="str">
+        <v>김기사</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>△△건설</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>창호 양중</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H5" s="16" t="n">
         <f aca="false">IF(OR($F5="",$G5=""),"",ROUND(IF($G5&lt;1,$G5*24,INT($G5/100)+MOD($G5,100)/60)-IF($F5&lt;1,$F5*24,INT($F5/100)+MOD($F5,100)/60),2))</f>
-        <v/>
-      </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="18" t="str">
+        <v>4</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J5" s="18" t="n">
         <f aca="false">IF(OR($H5="",$I5=""),"",ROUND($H5*$I5,0))</f>
-        <v/>
+        <v>480000</v>
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="17"/>
-      <c r="M5" s="18" t="str">
+      <c r="M5" s="18" t="n">
         <f aca="false">IF($J5="","",$J5-IF($L5="",0,$L5))</f>
-        <v/>
-      </c>
-      <c r="N5" s="19" t="str">
+        <v>480000</v>
+      </c>
+      <c r="N5" s="19" t="n">
         <f aca="true">IF(OR($A5="",$M5="",$M5&lt;=0),"",TODAY()-$A5)</f>
-        <v/>
-      </c>
-      <c r="O5" s="20" t="str">
+        <v>25</v>
+      </c>
+      <c r="O5" s="20" t="n">
         <f aca="false">IF($B5="","",IFERROR(INDEX(차량목록!$D$3:$D$42,MATCH($B5,차량목록!$A$3:$A$42,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P5" s="18" t="str">
+        <v>0.25</v>
+      </c>
+      <c r="P5" s="18" t="n">
         <f aca="false">IF($J5="","",ROUND($J5*$O5,0))</f>
-        <v/>
+        <v>120000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13"/>
-      <c r="B6" s="10"/>
+      <c r="A6" s="13" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>경기00가5678</t>
+        </is>
+      </c>
       <c r="C6" s="14" t="str">
         <f aca="false">IF($B6="","",IFERROR(INDEX(차량목록!$B$3:$B$42,MATCH($B6,차량목록!$A$3:$A$42,0)),"미등록차량"))</f>
-        <v/>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="16" t="str">
+        <v>이기사</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>△△건설</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>PC 슬래브 설치</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>830</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>1730</v>
+      </c>
+      <c r="H6" s="16" t="n">
         <f aca="false">IF(OR($F6="",$G6=""),"",ROUND(IF($G6&lt;1,$G6*24,INT($G6/100)+MOD($G6,100)/60)-IF($F6&lt;1,$F6*24,INT($F6/100)+MOD($F6,100)/60),2))</f>
-        <v/>
-      </c>
-      <c r="I6" s="17"/>
-      <c r="J6" s="18" t="str">
+        <v>9</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J6" s="18" t="n">
         <f aca="false">IF(OR($H6="",$I6=""),"",ROUND($H6*$I6,0))</f>
-        <v/>
+        <v>1350000</v>
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="17"/>
-      <c r="M6" s="18" t="str">
+      <c r="M6" s="18" t="n">
         <f aca="false">IF($J6="","",$J6-IF($L6="",0,$L6))</f>
-        <v/>
-      </c>
-      <c r="N6" s="19" t="str">
+        <v>1350000</v>
+      </c>
+      <c r="N6" s="19" t="n">
         <f aca="true">IF(OR($A6="",$M6="",$M6&lt;=0),"",TODAY()-$A6)</f>
-        <v/>
-      </c>
-      <c r="O6" s="20" t="str">
+        <v>11</v>
+      </c>
+      <c r="O6" s="20" t="n">
         <f aca="false">IF($B6="","",IFERROR(INDEX(차량목록!$D$3:$D$42,MATCH($B6,차량목록!$A$3:$A$42,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P6" s="18" t="str">
+        <v>0.2</v>
+      </c>
+      <c r="P6" s="18" t="n">
         <f aca="false">IF($J6="","",ROUND($J6*$O6,0))</f>
-        <v/>
+        <v>270000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13"/>
-      <c r="B7" s="10"/>
+      <c r="A7" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>경기00가1234</t>
+        </is>
+      </c>
       <c r="C7" s="14" t="str">
         <f aca="false">IF($B7="","",IFERROR(INDEX(차량목록!$B$3:$B$42,MATCH($B7,차량목록!$A$3:$A$42,0)),"미등록차량"))</f>
-        <v/>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16" t="str">
+        <v>김기사</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>○○종합건설</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>외벽 패널 양중</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H7" s="16" t="n">
         <f aca="false">IF(OR($F7="",$G7=""),"",ROUND(IF($G7&lt;1,$G7*24,INT($G7/100)+MOD($G7,100)/60)-IF($F7&lt;1,$F7*24,INT($F7/100)+MOD($F7,100)/60),2))</f>
-        <v/>
-      </c>
-      <c r="I7" s="17"/>
-      <c r="J7" s="18" t="str">
+        <v>7</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J7" s="18" t="n">
         <f aca="false">IF(OR($H7="",$I7=""),"",ROUND($H7*$I7,0))</f>
-        <v/>
+        <v>840000</v>
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="17"/>
-      <c r="M7" s="18" t="str">
+      <c r="M7" s="18" t="n">
         <f aca="false">IF($J7="","",$J7-IF($L7="",0,$L7))</f>
-        <v/>
-      </c>
-      <c r="N7" s="19" t="str">
+        <v>840000</v>
+      </c>
+      <c r="N7" s="19" t="n">
         <f aca="true">IF(OR($A7="",$M7="",$M7&lt;=0),"",TODAY()-$A7)</f>
-        <v/>
-      </c>
-      <c r="O7" s="20" t="str">
+        <v>4</v>
+      </c>
+      <c r="O7" s="20" t="n">
         <f aca="false">IF($B7="","",IFERROR(INDEX(차량목록!$D$3:$D$42,MATCH($B7,차량목록!$A$3:$A$42,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P7" s="18" t="str">
+        <v>0.25</v>
+      </c>
+      <c r="P7" s="18" t="n">
         <f aca="false">IF($J7="","",ROUND($J7*$O7,0))</f>
-        <v/>
+        <v>210000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21464,23 +21580,23 @@
       </c>
       <c r="C3" s="21" t="n">
         <f aca="false">IF($A3="","",COUNTIFS(배차일보!$B$3:$B$502,$A3))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3" s="16" t="n">
         <f aca="false">IF($A3="","",ROUND(SUMIFS(배차일보!$H$3:$H$502,배차일보!$B$3:$B$502,$A3),2))</f>
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="E3" s="18" t="n">
         <f aca="false">IF($A3="","",SUMIFS(배차일보!$J$3:$J$502,배차일보!$B$3:$B$502,$A3))</f>
-        <v>0</v>
+        <v>2460000</v>
       </c>
       <c r="F3" s="18" t="n">
         <f aca="false">IF($A3="","",SUMIFS(배차일보!$L$3:$L$502,배차일보!$B$3:$B$502,$A3))</f>
-        <v>0</v>
+        <v>1140000</v>
       </c>
       <c r="G3" s="18" t="n">
         <f aca="false">IF($A3="","",$E3-$F3)</f>
-        <v>0</v>
+        <v>1320000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21494,15 +21610,15 @@
       </c>
       <c r="C4" s="21" t="n">
         <f aca="false">IF($A4="","",COUNTIFS(배차일보!$B$3:$B$502,$A4))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" s="16" t="n">
         <f aca="false">IF($A4="","",ROUND(SUMIFS(배차일보!$H$3:$H$502,배차일보!$B$3:$B$502,$A4),2))</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E4" s="18" t="n">
         <f aca="false">IF($A4="","",SUMIFS(배차일보!$J$3:$J$502,배차일보!$B$3:$B$502,$A4))</f>
-        <v>0</v>
+        <v>2700000</v>
       </c>
       <c r="F4" s="18" t="n">
         <f aca="false">IF($A4="","",SUMIFS(배차일보!$L$3:$L$502,배차일보!$B$3:$B$502,$A4))</f>
@@ -21510,7 +21626,7 @@
       </c>
       <c r="G4" s="18" t="n">
         <f aca="false">IF($A4="","",$E4-$F4)</f>
-        <v>0</v>
+        <v>2700000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22659,23 +22775,23 @@
       </c>
       <c r="C44" s="23" t="n">
         <f aca="false">SUM(C3:C42)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D44" s="24" t="n">
         <f aca="false">SUM(D3:D42)</f>
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="E44" s="23" t="n">
         <f aca="false">SUM(E3:E42)</f>
-        <v>0</v>
+        <v>5160000</v>
       </c>
       <c r="F44" s="23" t="n">
         <f aca="false">SUM(F3:F42)</f>
-        <v>0</v>
+        <v>1140000</v>
       </c>
       <c r="G44" s="23" t="n">
         <f aca="false">SUM(G3:G42)</f>
-        <v>0</v>
+        <v>4020000</v>
       </c>
     </row>
   </sheetData>
@@ -22748,57 +22864,57 @@
       </c>
       <c r="B3" s="21" t="n">
         <f aca="false">IF($A3="","",COUNTIFS(배차일보!$D$3:$D$502,$A3))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C3" s="18" t="n">
         <f aca="false">IF($A3="","",SUMIFS(배차일보!$J$3:$J$502,배차일보!$D$3:$D$502,$A3))</f>
-        <v>0</v>
+        <v>3330000</v>
       </c>
       <c r="D3" s="18" t="n">
         <f aca="false">IF($A3="","",SUMIFS(배차일보!$L$3:$L$502,배차일보!$D$3:$D$502,$A3))</f>
-        <v>0</v>
+        <v>1140000</v>
       </c>
       <c r="E3" s="18" t="n">
         <f aca="false">IF($A3="","",$C3-$D3)</f>
-        <v>0</v>
+        <v>2190000</v>
       </c>
       <c r="F3" s="21" t="n">
         <f aca="false">IF($A3="","",COUNTIFS(배차일보!$D$3:$D$502,$A3,배차일보!$M$3:$M$502,"&gt;0"))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="19" t="n">
         <f aca="true">IF($A3="","",IF($F3=0,0,TODAY()-_xlfn.MINIFS(배차일보!$A$3:$A$502,배차일보!$D$3:$D$502,$A3,배차일보!$M$3:$M$502,"&gt;0")))</f>
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="str">
         <f aca="false">IF(거래처목록!$A4="","",거래처목록!$A4)</f>
-        <v/>
-      </c>
-      <c r="B4" s="21" t="str">
+        <v>△△건설</v>
+      </c>
+      <c r="B4" s="21" t="n">
         <f aca="false">IF($A4="","",COUNTIFS(배차일보!$D$3:$D$502,$A4))</f>
-        <v/>
-      </c>
-      <c r="C4" s="18" t="str">
+        <v>2</v>
+      </c>
+      <c r="C4" s="18" t="n">
         <f aca="false">IF($A4="","",SUMIFS(배차일보!$J$3:$J$502,배차일보!$D$3:$D$502,$A4))</f>
-        <v/>
-      </c>
-      <c r="D4" s="18" t="str">
+        <v>1830000</v>
+      </c>
+      <c r="D4" s="18" t="n">
         <f aca="false">IF($A4="","",SUMIFS(배차일보!$L$3:$L$502,배차일보!$D$3:$D$502,$A4))</f>
-        <v/>
-      </c>
-      <c r="E4" s="18" t="str">
+        <v>0</v>
+      </c>
+      <c r="E4" s="18" t="n">
         <f aca="false">IF($A4="","",$C4-$D4)</f>
-        <v/>
-      </c>
-      <c r="F4" s="21" t="str">
+        <v>1830000</v>
+      </c>
+      <c r="F4" s="21" t="n">
         <f aca="false">IF($A4="","",COUNTIFS(배차일보!$D$3:$D$502,$A4,배차일보!$M$3:$M$502,"&gt;0"))</f>
-        <v/>
-      </c>
-      <c r="G4" s="19" t="str">
+        <v>2</v>
+      </c>
+      <c r="G4" s="19" t="n">
         <f aca="true">IF($A4="","",IF($F4=0,0,TODAY()-_xlfn.MINIFS(배차일보!$A$3:$A$502,배차일보!$D$3:$D$502,$A4,배차일보!$M$3:$M$502,"&gt;0")))</f>
-        <v/>
+        <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24547,23 +24663,23 @@
       </c>
       <c r="B64" s="22" t="n">
         <f aca="false">SUM(B3:B62)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C64" s="23" t="n">
         <f aca="false">SUM(C3:C62)</f>
-        <v>0</v>
+        <v>5160000</v>
       </c>
       <c r="D64" s="23" t="n">
         <f aca="false">SUM(D3:D62)</f>
-        <v>0</v>
+        <v>1140000</v>
       </c>
       <c r="E64" s="23" t="n">
         <f aca="false">SUM(E3:E62)</f>
-        <v>0</v>
+        <v>4020000</v>
       </c>
       <c r="F64" s="22" t="n">
         <f aca="false">SUM(F3:F62)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
